--- a/Tagihan/2026/Agustus/H Jani.xlsx
+++ b/Tagihan/2026/Agustus/H Jani.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\2026\Agustus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E62B758-0C16-40F5-9B6A-137DF123742A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{606024E7-4F63-4FD4-B462-F0BEBD21DEEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,8 +30,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>NO.</t>
   </si>
@@ -84,7 +106,28 @@
     <t>Lot</t>
   </si>
   <si>
-    <t xml:space="preserve">Kepada Tuan/Nyonya   </t>
+    <t>Paket Ezviz H8c Pro 4mp + Memory 64GB</t>
+  </si>
+  <si>
+    <t>Set</t>
+  </si>
+  <si>
+    <t>Mtr</t>
+  </si>
+  <si>
+    <t>Reposisi Kamera</t>
+  </si>
+  <si>
+    <t>Rumah</t>
+  </si>
+  <si>
+    <t>Kabel CCTV Hitam</t>
+  </si>
+  <si>
+    <t>Konnektor</t>
+  </si>
+  <si>
+    <t>Bengkel Marido</t>
   </si>
   <si>
     <r>
@@ -98,29 +141,14 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> 25 Agustus 2026</t>
+      <t xml:space="preserve"> 27 Agustus 2026</t>
     </r>
   </si>
   <si>
-    <t>Paket Ezviz H8c Pro 4mp + Memory 64GB</t>
-  </si>
-  <si>
-    <t>Perbaikan CCTV</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> *Kabel CCTV Warna Hitam</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> *Konnektor</t>
-  </si>
-  <si>
-    <t>Set</t>
-  </si>
-  <si>
-    <t>Mtr</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> *Reposisi Kamera</t>
+    <t>Kepada Tuan/Nyonya   H Jani</t>
+  </si>
+  <si>
+    <t>Biaya Perbaikan</t>
   </si>
 </sst>
 </file>
@@ -130,7 +158,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,6 +236,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -217,7 +253,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -367,9 +403,7 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -382,9 +416,7 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -395,9 +427,20 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -408,9 +451,7 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -423,22 +464,31 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
+      <left/>
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -447,7 +497,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -467,9 +517,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -522,13 +569,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -578,6 +625,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -652,13 +711,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>59532</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2403475</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>115571</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -993,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B5:H37"/>
+  <dimension ref="B5:I44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
@@ -1009,47 +1068,47 @@
     <row r="5" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
     </row>
     <row r="8" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
     </row>
     <row r="9" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
     </row>
     <row r="10" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
     </row>
     <row r="11" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
     </row>
     <row r="12" spans="2:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F12" s="7"/>
@@ -1059,36 +1118,36 @@
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="47"/>
+      <c r="F13" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="46"/>
     </row>
     <row r="14" spans="2:7" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="48" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="48"/>
+      <c r="F14" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="47"/>
     </row>
     <row r="15" spans="2:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="23"/>
-      <c r="D15" s="24"/>
-    </row>
-    <row r="16" spans="2:7" s="1" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="27" t="s">
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+    </row>
+    <row r="16" spans="2:7" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D16" s="29" t="s">
+      <c r="D16" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="29" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="30" t="s">
@@ -1098,221 +1157,319 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="25">
+    <row r="17" spans="2:7" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="50"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+    </row>
+    <row r="18" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="24">
         <v>1</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C18" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="24">
+        <v>2</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="14">
+        <v>1350000</v>
+      </c>
+      <c r="G18" s="14">
+        <f t="shared" ref="G18:G21" si="0">F18*D18</f>
+        <v>2700000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="24">
+        <v>2</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="24">
+        <v>3</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="13">
+        <v>75000</v>
+      </c>
+      <c r="G19" s="14">
+        <f t="shared" si="0"/>
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="2">
+        <v>3</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="24">
+        <v>25</v>
+      </c>
+      <c r="E20" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="25">
+      <c r="F20" s="13">
+        <v>5000</v>
+      </c>
+      <c r="G20" s="14">
+        <f t="shared" si="0"/>
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="2">
+        <v>4</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="24">
+        <v>2</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="13">
+        <v>15000</v>
+      </c>
+      <c r="G21" s="14">
+        <f t="shared" si="0"/>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="52"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="14"/>
+    </row>
+    <row r="23" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="13">
+        <v>1350000</v>
+      </c>
+      <c r="G23" s="14">
+        <f>F23*D23</f>
+        <v>1350000</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="2">
+        <v>2</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="2">
+        <v>11</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="13">
+        <v>5000</v>
+      </c>
+      <c r="G24" s="14">
+        <f>F24*D24</f>
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="2">
         <v>3</v>
       </c>
-      <c r="E17" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="15">
-        <v>1100000</v>
-      </c>
-      <c r="G17" s="15">
-        <f t="shared" ref="G17:G21" si="0">F17*D17</f>
-        <v>3300000</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="2">
-        <v>2</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="15"/>
-    </row>
-    <row r="19" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="2"/>
-      <c r="C19" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="2">
-        <v>36</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="14">
-        <v>5000</v>
-      </c>
-      <c r="G19" s="15">
-        <f>F19*D19</f>
-        <v>180000</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="2"/>
-      <c r="C20" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="2">
-        <v>3</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="C25" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="13">
+        <v>15000</v>
+      </c>
+      <c r="G25" s="14">
+        <f>F25*D25</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="2">
+        <v>4</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="14">
-        <v>100000</v>
-      </c>
-      <c r="G20" s="15">
-        <f>F20*D20</f>
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="2"/>
-      <c r="C21" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="2">
-        <v>3</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" s="14">
-        <v>15000</v>
-      </c>
-      <c r="G21" s="15">
-        <f>F21*D21</f>
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="2"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="16"/>
-    </row>
-    <row r="23" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="2"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="16"/>
-    </row>
-    <row r="24" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="2"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="16"/>
-    </row>
-    <row r="25" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="2"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="16"/>
-    </row>
-    <row r="26" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="2"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="16"/>
+      <c r="F26" s="13">
+        <v>75000</v>
+      </c>
+      <c r="G26" s="15">
+        <f>F26*D26</f>
+        <v>75000</v>
+      </c>
     </row>
     <row r="27" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="2"/>
-      <c r="C27" s="17"/>
+      <c r="C27" s="16"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="13"/>
       <c r="G27" s="15"/>
     </row>
-    <row r="28" spans="2:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="42" t="s">
+    <row r="28" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="2"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="15"/>
+    </row>
+    <row r="29" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="2"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="15"/>
+    </row>
+    <row r="30" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="2"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="15"/>
+    </row>
+    <row r="31" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="2"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="32" spans="2:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="43"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="18">
-        <f>SUM(G17:G27)</f>
-        <v>3825000</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="8"/>
-    </row>
-    <row r="31" spans="2:7" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B31" s="45" t="s">
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="17">
+        <f>SUM(G18:G31)</f>
+        <v>4575000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="8"/>
+    </row>
+    <row r="35" spans="2:9" s="9" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B35" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="45"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="46" t="s">
+      <c r="C35" s="44"/>
+      <c r="D35" s="20"/>
+      <c r="E35"/>
+      <c r="F35" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="46"/>
-    </row>
-    <row r="35" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="40" t="s">
+      <c r="G35" s="45"/>
+    </row>
+    <row r="39" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B39" s="35"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="35"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B40" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="12"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="37" t="s">
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="11"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="12"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="11"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I44" cm="1">
+        <f t="array" aca="1" ref="I44" ca="1">A2:I44</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
     <mergeCell ref="C7:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B41:G41"/>
     <mergeCell ref="C11:G11"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="F35:G35"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.23622047244094491" top="7.874015748031496E-2" bottom="0.74803149606299213" header="0.59055118110236227" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="85" orientation="portrait" horizontalDpi="4294967294" verticalDpi="300" r:id="rId1"/>
